--- a/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 10,76</t>
+          <t>-21,76; 9,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,79; 15,12</t>
+          <t>-14,67; 14,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 14,31</t>
+          <t>-28,69; 15,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-37,65; 10,06</t>
+          <t>-36,45; 10,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,63; 17,33</t>
+          <t>-27,35; 15,44</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 23,61</t>
+          <t>-17,79; 22,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,81; 23,1</t>
+          <t>-37,46; 25,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-42,05; 12,14</t>
+          <t>-41,92; 12,49</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -1,15</t>
+          <t>-14,67; -0,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,69; 2,61</t>
+          <t>-10,75; 3,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 0,65</t>
+          <t>-11,46; 0,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 10,3</t>
+          <t>-2,17; 10,02</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,11; -1,66</t>
+          <t>-19,72; -0,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 3,71</t>
+          <t>-14,23; 4,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 0,93</t>
+          <t>-14,04; 1,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 13,52</t>
+          <t>-2,52; 13,05</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,16; 14,47</t>
+          <t>-8,11; 15,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,37; 3,29</t>
+          <t>-16,3; 2,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 18,41</t>
+          <t>-2,16; 19,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,38; -2,16</t>
+          <t>-19,78; -1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 21,53</t>
+          <t>-10,28; 23,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 4,1</t>
+          <t>-18,68; 3,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 29,38</t>
+          <t>-2,77; 30,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,8; -2,52</t>
+          <t>-21,8; -1,63</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 0,12</t>
+          <t>-11,19; 0,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,63</t>
+          <t>-9,38; 0,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,89</t>
+          <t>-7,32; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,52</t>
+          <t>-5,38; 4,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,12</t>
+          <t>-15,04; 0,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,29</t>
+          <t>-11,88; 1,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,96</t>
+          <t>-9,33; 4,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,69</t>
+          <t>-6,28; 5,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 9,61</t>
+          <t>-22,03; 10,99</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,67; 14,98</t>
+          <t>-14,26; 16,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-28,69; 15,03</t>
+          <t>-30,54; 13,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-36,45; 10,05</t>
+          <t>-35,13; 11,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 15,44</t>
+          <t>-28,7; 18,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 22,74</t>
+          <t>-17,79; 25,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,46; 25,09</t>
+          <t>-40,45; 21,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-41,92; 12,49</t>
+          <t>-38,57; 13,41</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,67; -0,4</t>
+          <t>-14,55; -0,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 3,07</t>
+          <t>-11,2; 2,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 0,93</t>
+          <t>-12,28; 0,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 10,02</t>
+          <t>-2,95; 9,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,72; -0,74</t>
+          <t>-19,9; -0,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 4,3</t>
+          <t>-14,42; 4,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 1,26</t>
+          <t>-15,13; 0,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 13,05</t>
+          <t>-3,54; 13,03</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,11; 15,76</t>
+          <t>-9,22; 14,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,3; 2,65</t>
+          <t>-15,82; 4,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 19,43</t>
+          <t>-2,58; 18,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; -1,4</t>
+          <t>-18,78; -0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,28; 23,45</t>
+          <t>-11,61; 21,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,68; 3,28</t>
+          <t>-17,92; 5,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 30,62</t>
+          <t>-3,44; 29,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-21,8; -1,63</t>
+          <t>-20,91; -1,12</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 0,11</t>
+          <t>-10,88; -0,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,99</t>
+          <t>-9,08; 1,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,1</t>
+          <t>-7,85; 2,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,11</t>
+          <t>-5,83; 3,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 0,17</t>
+          <t>-14,73; -0,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 1,32</t>
+          <t>-11,64; 2,24</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,2</t>
+          <t>-9,8; 3,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,12</t>
+          <t>-7,0; 4,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,88</t>
+          <t>-2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,44%</t>
+          <t>-2,66%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 10,99</t>
+          <t>-21,56; 10,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 16,32</t>
+          <t>-14,79; 15,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,54; 13,7</t>
+          <t>-27,57; 14,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-35,13; 11,02</t>
+          <t>-20,02; 15,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-28,7; 18,19</t>
+          <t>-27,63; 17,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,79; 25,53</t>
+          <t>-17,99; 23,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-40,45; 21,62</t>
+          <t>-36,81; 23,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-38,57; 13,41</t>
+          <t>-21,98; 20,47</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,98</t>
+          <t>3,35</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,55; -0,66</t>
+          <t>-14,96; -1,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 2,85</t>
+          <t>-10,69; 2,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 0,44</t>
+          <t>-12,04; 0,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 9,88</t>
+          <t>-3,28; 9,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,9; -0,99</t>
+          <t>-20,11; -1,66</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 4,08</t>
+          <t>-13,9; 3,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,13; 0,69</t>
+          <t>-14,98; 0,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 13,03</t>
+          <t>-3,94; 12,29</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-10,42</t>
+          <t>-10,52</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-11,91%</t>
+          <t>-12,01%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 14,27</t>
+          <t>-9,16; 14,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,82; 4,79</t>
+          <t>-16,37; 3,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 18,81</t>
+          <t>-2,43; 18,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-18,78; -0,9</t>
+          <t>-19,54; -2,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 21,3</t>
+          <t>-11,25; 21,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,92; 5,95</t>
+          <t>-18,68; 4,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 29,01</t>
+          <t>-3,02; 29,38</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-20,91; -1,12</t>
+          <t>-21,96; -3,15</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-0,9%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,03</t>
+          <t>-10,68; 0,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,67</t>
+          <t>-8,99; 1,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,65</t>
+          <t>-7,57; 2,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,9</t>
+          <t>-5,21; 4,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -0,15</t>
+          <t>-14,6; 0,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 2,24</t>
+          <t>-11,43; 2,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 3,68</t>
+          <t>-9,64; 3,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,86</t>
+          <t>-6,15; 5,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-5,88</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-6,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,25</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,33%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-0,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-8,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-2,66%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-5.875717741737486</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.4245093018364288</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-6.164459927021248</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.250225112784854</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.08329492496760663</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.005723341592240093</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.08872340661069397</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.02656530355925361</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-21,56; 10,76</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-14,79; 15,12</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-27,57; 14,31</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-20,02; 15,24</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-27,63; 17,33</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-17,99; 23,61</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-36,81; 23,1</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-21,98; 20,47</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-21.5626386119737</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-14.7937893624599</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-27.56752621047775</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-20.01900960193237</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2763227886964278</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1798901521429471</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.368141835050769</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.2198171324528346</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>10.76418532240234</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.11767831181942</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>14.3144915435856</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>15.24263294901032</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.1733457452257323</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2361360457684278</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.2310317365983114</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.2047025540774318</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-7,77</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-4,03</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-5,61</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,35</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-10,96%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-5,48%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-7,17%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>4,17%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-14,96; -1,15</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-10,69; 2,61</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-12,04; 0,65</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,28; 9,56</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-20,11; -1,66</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-13,9; 3,71</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-14,98; 0,93</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-3,94; 12,29</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-7.768949296118688</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-4.025475265694234</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-5.614738050632262</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3.352351741175574</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1095511549498757</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.05479623260550826</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.07168565555636951</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.04173242333237077</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>-6,11</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>7,68</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-10,52</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,78%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-7,25%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,81%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-12,01%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-14.9622725769091</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-10.68598053791677</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-12.03980787230985</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.277417360868291</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.2010536810424559</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.1390098296715194</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1498423331551947</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.03938065198698384</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,16; 14,47</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-16,37; 3,29</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-2,43; 18,41</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-19,54; -2,64</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-11,25; 21,53</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-18,68; 4,1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-3,02; 29,38</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-21,96; -3,15</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>-1.150812474899641</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>2.606356630424329</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.6463860860558583</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>9.558057643153287</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>-0.01658317482182825</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.03706465722407162</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.009292574286575074</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.1228826599857619</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +819,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,21</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,85</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-7,3%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-5,06%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>2.778658328864791</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-6.112765150680532</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>7.679095541540537</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-10.51558936013878</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.03782906973132697</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>-0.07248304014143533</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.1080866783231516</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.120097975372489</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-10,68; 0,12</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; 1,63</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-7,57; 2,89</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; 4,71</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-14,6; 0,12</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-11,43; 2,29</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-9,64; 3,96</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-6,15; 5,87</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.161991590333665</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-16.37410176133628</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-2.428349347376142</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-19.54157001543819</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1124700118474502</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1867774702742179</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.03024182058445903</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2196220618050989</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>14.4682242470664</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.294386894144084</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>18.41382373443741</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>-2.639070976609609</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2152532597916024</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.04102280447498844</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.2937659056843428</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>-0.03151365610194387</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.212416755683913</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.847131579083996</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.346113532139593</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.6911477863691395</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.0730189106317876</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.0506364186767898</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.03090186111261805</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.008371939748779599</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-10.68446303506486</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-8.989965860777467</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-7.569255816311143</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.20983897919485</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1460294691063848</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.1142622404113307</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.09636095031837134</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.06145701801176513</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.1205785602458333</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.633280847582105</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.890588730925806</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.707408935664438</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.001174760394097873</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02290626049578703</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.03962332347630908</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.05865344595378109</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1017,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
